--- a/participants-sample.xlsx
+++ b/participants-sample.xlsx
@@ -1,41 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hoangth/Documents/lucky-draw/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6934C383-AADA-6D48-8DE0-C9501C6AD68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Mã nhân viên</t>
+  </si>
+  <si>
+    <t>Họ tên</t>
+  </si>
+  <si>
+    <t>NV001</t>
+  </si>
+  <si>
+    <t>NV002</t>
+  </si>
+  <si>
+    <t>NV003</t>
+  </si>
+  <si>
+    <t>NV004</t>
+  </si>
+  <si>
+    <t>Phạm Minh Đức</t>
+  </si>
+  <si>
+    <t>NV005</t>
+  </si>
+  <si>
+    <t>Hoàng Thu Hà</t>
+  </si>
+  <si>
+    <t>NV006</t>
+  </si>
+  <si>
+    <t>Vũ Đình Khôi</t>
+  </si>
+  <si>
+    <t>NV007</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Lan</t>
+  </si>
+  <si>
+    <t>NV008</t>
+  </si>
+  <si>
+    <t>Bùi Xuân Minh</t>
+  </si>
+  <si>
+    <t>NV009</t>
+  </si>
+  <si>
+    <t>Đặng Thu Nga</t>
+  </si>
+  <si>
+    <t>Sử Minh</t>
+  </si>
+  <si>
+    <t>Huy</t>
+  </si>
+  <si>
+    <t>Huy Hoàng</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +116,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,8 +455,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -405,89 +465,90 @@
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Mã nhân viên</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Họ tên</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>NV001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Nguyễn Văn An</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>NV002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Trần Thị Bình</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>NV003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Lê Hoàng Cường</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>NV004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Phạm Minh Đức</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>NV005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Hoàng Thu Hà</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>NV006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Vũ Đình Khôi</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>NV007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Đỗ Thị Lan</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>NV008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Bùi Xuân Minh</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>NV009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Đặng Thu Nga</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError sqref="A1:B1 A5:B10 A2 A3 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>